--- a/obras/teste_rev00.xlsx
+++ b/obras/teste_rev00.xlsx
@@ -1431,7 +1431,9 @@
           <t>Número de equipes:</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n"/>
+      <c r="E7" s="20" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="20" t="n"/>
       <c r="G7" s="20" t="n"/>
       <c r="H7" s="20" t="n"/>
@@ -1464,7 +1466,9 @@
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="44" t="n"/>
       <c r="D10" s="65" t="n"/>
-      <c r="E10" s="44" t="n"/>
+      <c r="E10" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="65" t="n"/>
       <c r="G10" s="60" t="n"/>
       <c r="H10" s="61" t="n"/>
@@ -1518,7 +1522,9 @@
       <c r="B14" s="33" t="n"/>
       <c r="C14" s="13" t="n"/>
       <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="13" t="n"/>
       <c r="H14" s="13" t="n"/>

--- a/obras/teste_rev00.xlsx
+++ b/obras/teste_rev00.xlsx
@@ -1363,7 +1363,7 @@
       </c>
       <c r="I3" s="49" t="inlineStr">
         <is>
-          <t>Joinville</t>
+          <t>Curitiba</t>
         </is>
       </c>
       <c r="J3" s="65" t="n"/>
